--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\MCA\CAP776_Python\Demo\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AAB07F-8E10-4648-98CD-EDE108DC47BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E8B884-F509-4090-8014-727618CDCB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very pleasant day , without laziness </t>
   </si>
 </sst>
 </file>
@@ -1013,29 +1025,51 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
-        <v>46223</v>
-      </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+        <v>46230</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <v>250</v>
+      </c>
+      <c r="G7" s="14">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14">
+        <v>120</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\MCA\CAP776_Python\Demo\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E8B884-F509-4090-8014-727618CDCB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E51CF8-51CA-4FEF-B9B1-40C5F1CCDC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,12 @@
   </si>
   <si>
     <t xml:space="preserve">Very pleasant day , without laziness </t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average </t>
   </si>
 </sst>
 </file>
@@ -1072,26 +1078,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46234</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>120</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
